--- a/articles.xlsx
+++ b/articles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t xml:space="preserve">generated</t>
   </si>
@@ -127,7 +127,16 @@
     <t xml:space="preserve">Shadows of Kerr–de Sitter naked singularities</t>
   </si>
   <si>
+    <t xml:space="preserve">Nahé singularity: Když vesmír odloží svůj černý závoj</t>
+  </si>
+  <si>
     <t xml:space="preserve">Charbulák</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light escape cones in the locally nonrotating reference frames of the Kerr–de Sitter superspinars and related superspinar shadows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stíny bez horizontu událostí: Jak čeští fyzici modelují optické podpisy strunových superspinarů</t>
   </si>
 </sst>
 </file>
@@ -241,8 +250,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I84"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="32.29"/>
@@ -252,7 +261,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="40.29"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -281,7 +290,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -305,7 +314,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -329,7 +338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -353,7 +362,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -377,7 +386,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
@@ -401,112 +410,164 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C16" s="4"/>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C20" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C21" s="4"/>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C22" s="4"/>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="4"/>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C28" s="4"/>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C30" s="4"/>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="84" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
